--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -14960,16 +14960,16 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27251</v>
+        <v>27273</v>
       </c>
       <c r="O81" t="n">
-        <v>27251</v>
+        <v>27273</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>100.0877948937338</v>
+        <v>100.1685967537633</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16244,16 +16244,16 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>4671</v>
+        <v>5429</v>
       </c>
       <c r="O89" t="n">
-        <v>4671</v>
+        <v>5429</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>17.15570400897694</v>
+        <v>19.93969536817294</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>145145</v>
+        <v>145925</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13824,16 +13824,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25542</v>
+        <v>25543</v>
       </c>
       <c r="O74" t="n">
-        <v>25542</v>
+        <v>25543</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>93.81095949417447</v>
+        <v>93.814632305994</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14960,16 +14960,16 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27273</v>
+        <v>27302</v>
       </c>
       <c r="O81" t="n">
-        <v>27273</v>
+        <v>27302</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>100.1685967537633</v>
+        <v>100.2751082965293</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16244,16 +16244,16 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5429</v>
+        <v>6202</v>
       </c>
       <c r="O89" t="n">
-        <v>5429</v>
+        <v>6202</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>19.93969536817294</v>
+        <v>22.77877890466174</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>145925</v>
+        <v>146728</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13824,16 +13824,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25543</v>
+        <v>25544</v>
       </c>
       <c r="O74" t="n">
-        <v>25543</v>
+        <v>25544</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>93.814632305994</v>
+        <v>93.81830511781352</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14960,16 +14960,16 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27302</v>
+        <v>27329</v>
       </c>
       <c r="O81" t="n">
-        <v>27302</v>
+        <v>27329</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>100.2751082965293</v>
+        <v>100.3742742156563</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16244,16 +16244,16 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>6202</v>
+        <v>6980</v>
       </c>
       <c r="O89" t="n">
-        <v>6202</v>
+        <v>6980</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>22.77877890466174</v>
+        <v>25.63622650024813</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16718,6 +16718,154 @@
       <c r="BC91" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>1155</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.94341371073846</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16902,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16985,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -16847,7 +16995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -16899,7 +17047,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>146728</v>
+        <v>148689</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>249</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>4.429234835451702</v>
       </c>
@@ -1312,9 +1309,6 @@
       <c r="P5" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -1862,9 +1856,6 @@
       <c r="P8" t="n">
         <v>9</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -2412,9 +2403,6 @@
       <c r="P11" t="n">
         <v>21</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>5.219608827601292</v>
       </c>
@@ -2962,9 +2950,6 @@
       <c r="P14" t="n">
         <v>30</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>7.456584039430417</v>
       </c>
@@ -3657,9 +3642,6 @@
       <c r="O18" t="n">
         <v>682</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>12.13147854529342</v>
       </c>
@@ -4056,9 +4038,6 @@
       <c r="P20" t="n">
         <v>26</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>6.462372834173028</v>
       </c>
@@ -4606,9 +4585,6 @@
       <c r="P23" t="n">
         <v>19</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -5156,9 +5132,6 @@
       <c r="P26" t="n">
         <v>15</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -5706,9 +5679,6 @@
       <c r="P29" t="n">
         <v>25</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>6.21382003285868</v>
       </c>
@@ -6401,9 +6371,6 @@
       <c r="O33" t="n">
         <v>1543</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>27.44702550643364</v>
       </c>
@@ -6800,9 +6767,6 @@
       <c r="P35" t="n">
         <v>13</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>3.231186417086514</v>
       </c>
@@ -7350,9 +7314,6 @@
       <c r="P38" t="n">
         <v>18</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>4.47395042365825</v>
       </c>
@@ -7900,9 +7861,6 @@
       <c r="P41" t="n">
         <v>15</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -8450,9 +8408,6 @@
       <c r="P44" t="n">
         <v>14</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>3.479739218400861</v>
       </c>
@@ -9000,9 +8955,6 @@
       <c r="P47" t="n">
         <v>7</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -9399,9 +9351,6 @@
       <c r="O49" t="n">
         <v>12101</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>44.44469582800898</v>
       </c>
@@ -9547,9 +9496,6 @@
       <c r="O50" t="n">
         <v>1139</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>20.26063645614253</v>
       </c>
@@ -10094,9 +10040,6 @@
       <c r="P53" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>2.485528013143472</v>
       </c>
@@ -10644,9 +10587,6 @@
       <c r="P56" t="n">
         <v>4</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.9942112052573888</v>
       </c>
@@ -11194,9 +11134,6 @@
       <c r="P59" t="n">
         <v>9</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -11744,9 +11681,6 @@
       <c r="P62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -12143,9 +12077,6 @@
       <c r="O64" t="n">
         <v>15962</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>58.62542226317489</v>
       </c>
@@ -12291,9 +12222,6 @@
       <c r="O65" t="n">
         <v>511</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>9.089714863115743</v>
       </c>
@@ -12838,9 +12766,6 @@
       <c r="P68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -13829,9 +13754,6 @@
       <c r="O74" t="n">
         <v>25544</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>93.81830511781352</v>
       </c>
@@ -13977,9 +13899,6 @@
       <c r="O75" t="n">
         <v>130</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>2.312451922123379</v>
       </c>
@@ -14373,9 +14292,6 @@
       <c r="O77" t="n">
         <v>737</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.6019877963759698</v>
       </c>
@@ -14521,9 +14437,6 @@
       <c r="O78" t="n">
         <v>682</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.5570633339598525</v>
       </c>
@@ -14669,9 +14582,6 @@
       <c r="O79" t="n">
         <v>788</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.6436450251618239</v>
       </c>
@@ -14817,9 +14727,6 @@
       <c r="O80" t="n">
         <v>885</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.7228754406957031</v>
       </c>
@@ -14965,9 +14872,6 @@
       <c r="O81" t="n">
         <v>27329</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>100.3742742156563</v>
       </c>
@@ -15113,9 +15017,6 @@
       <c r="O82" t="n">
         <v>22</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -15509,9 +15410,6 @@
       <c r="O84" t="n">
         <v>764</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.6240416233802455</v>
       </c>
@@ -15657,9 +15555,6 @@
       <c r="O85" t="n">
         <v>826</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.674683744649323</v>
       </c>
@@ -15805,9 +15700,6 @@
       <c r="O86" t="n">
         <v>976</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.7972050057841878</v>
       </c>
@@ -15953,9 +15845,6 @@
       <c r="O87" t="n">
         <v>1082</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.8837866969861591</v>
       </c>
@@ -16101,9 +15990,6 @@
       <c r="O88" t="n">
         <v>1027</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.8388622345700421</v>
       </c>
@@ -16249,9 +16135,6 @@
       <c r="O89" t="n">
         <v>6980</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>25.63622650024813</v>
       </c>
@@ -16397,9 +16280,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -16792,9 +16672,6 @@
       </c>
       <c r="O92" t="n">
         <v>1155</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0.94341371073846</v>

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25544</v>
+        <v>25545</v>
       </c>
       <c r="O74" t="n">
-        <v>25544</v>
+        <v>25545</v>
       </c>
       <c r="R74" t="n">
-        <v>93.81830511781352</v>
+        <v>93.82197792963304</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27329</v>
+        <v>27373</v>
       </c>
       <c r="O81" t="n">
-        <v>27329</v>
+        <v>27373</v>
       </c>
       <c r="R81" t="n">
-        <v>100.3742742156563</v>
+        <v>100.5358779357152</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>6980</v>
+        <v>8945</v>
       </c>
       <c r="O89" t="n">
-        <v>6980</v>
+        <v>8945</v>
       </c>
       <c r="R89" t="n">
-        <v>25.63622650024813</v>
+        <v>32.85330172560452</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>148689</v>
+        <v>150699</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25545</v>
+        <v>25546</v>
       </c>
       <c r="O74" t="n">
-        <v>25545</v>
+        <v>25546</v>
       </c>
       <c r="R74" t="n">
-        <v>93.82197792963304</v>
+        <v>93.82565074145256</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27373</v>
+        <v>27400</v>
       </c>
       <c r="O81" t="n">
-        <v>27373</v>
+        <v>27400</v>
       </c>
       <c r="R81" t="n">
-        <v>100.5358779357152</v>
+        <v>100.6350438548422</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>8945</v>
+        <v>9954</v>
       </c>
       <c r="O89" t="n">
-        <v>8945</v>
+        <v>9954</v>
       </c>
       <c r="R89" t="n">
-        <v>32.85330172560452</v>
+        <v>36.55916885149999</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>150699</v>
+        <v>151736</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27400</v>
+        <v>27420</v>
       </c>
       <c r="O81" t="n">
-        <v>27400</v>
+        <v>27420</v>
       </c>
       <c r="R81" t="n">
-        <v>100.6350438548422</v>
+        <v>100.7085000912326</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>9954</v>
+        <v>10684</v>
       </c>
       <c r="O89" t="n">
-        <v>9954</v>
+        <v>10684</v>
       </c>
       <c r="R89" t="n">
-        <v>36.55916885149999</v>
+        <v>39.24032147974944</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16741,6 +16741,151 @@
         </is>
       </c>
       <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1417</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1417</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.157417513520691</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16779,7 +16924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -16862,7 +17007,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -16872,7 +17017,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -16924,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>151736</v>
+        <v>153903</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27420</v>
+        <v>27429</v>
       </c>
       <c r="O81" t="n">
-        <v>27420</v>
+        <v>27429</v>
       </c>
       <c r="R81" t="n">
-        <v>100.7085000912326</v>
+        <v>100.7415553976083</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>10684</v>
+        <v>12229</v>
       </c>
       <c r="O89" t="n">
-        <v>10684</v>
+        <v>12229</v>
       </c>
       <c r="R89" t="n">
-        <v>39.24032147974944</v>
+        <v>44.91481574090751</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>153903</v>
+        <v>155457</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>12229</v>
+        <v>13043</v>
       </c>
       <c r="O89" t="n">
-        <v>12229</v>
+        <v>13043</v>
       </c>
       <c r="R89" t="n">
-        <v>44.91481574090751</v>
+        <v>47.90448456199663</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>155457</v>
+        <v>156271</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>13043</v>
+        <v>13313</v>
       </c>
       <c r="O89" t="n">
-        <v>13043</v>
+        <v>13313</v>
       </c>
       <c r="R89" t="n">
-        <v>47.90448456199663</v>
+        <v>48.89614375326697</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>156271</v>
+        <v>156541</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>13313</v>
+        <v>13518</v>
       </c>
       <c r="O89" t="n">
-        <v>13313</v>
+        <v>13518</v>
       </c>
       <c r="R89" t="n">
-        <v>48.89614375326697</v>
+        <v>49.64907017626852</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>156541</v>
+        <v>156746</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25546</v>
+        <v>25545</v>
       </c>
       <c r="O74" t="n">
-        <v>25546</v>
+        <v>25545</v>
       </c>
       <c r="R74" t="n">
-        <v>93.82565074145256</v>
+        <v>93.82197792963304</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>13518</v>
+        <v>14175</v>
       </c>
       <c r="O89" t="n">
-        <v>13518</v>
+        <v>14175</v>
       </c>
       <c r="R89" t="n">
-        <v>49.64907017626852</v>
+        <v>52.06210754169302</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>156746</v>
+        <v>157402</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>25545</v>
+        <v>25546</v>
       </c>
       <c r="O74" t="n">
-        <v>25545</v>
+        <v>25546</v>
       </c>
       <c r="R74" t="n">
-        <v>93.82197792963304</v>
+        <v>93.82565074145256</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27429</v>
+        <v>27443</v>
       </c>
       <c r="O81" t="n">
-        <v>27429</v>
+        <v>27443</v>
       </c>
       <c r="R81" t="n">
-        <v>100.7415553976083</v>
+        <v>100.7929747630816</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>14175</v>
+        <v>15692</v>
       </c>
       <c r="O89" t="n">
-        <v>14175</v>
+        <v>15692</v>
       </c>
       <c r="R89" t="n">
-        <v>52.06210754169302</v>
+        <v>57.63376307190455</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16275,13 +16275,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16434,10 +16434,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16886,6 +16886,151 @@
         </is>
       </c>
       <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>1067</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1067</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.8715345708726727</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16924,7 +17069,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17152,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -17017,7 +17162,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -17069,7 +17214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>157402</v>
+        <v>160002</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27443</v>
+        <v>27444</v>
       </c>
       <c r="O81" t="n">
-        <v>27443</v>
+        <v>27444</v>
       </c>
       <c r="R81" t="n">
-        <v>100.7929747630816</v>
+        <v>100.7966475749011</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>15692</v>
+        <v>16338</v>
       </c>
       <c r="O89" t="n">
-        <v>15692</v>
+        <v>16338</v>
       </c>
       <c r="R89" t="n">
-        <v>57.63376307190455</v>
+        <v>60.00639950731433</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>160002</v>
+        <v>160649</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>16338</v>
+        <v>17026</v>
       </c>
       <c r="O89" t="n">
-        <v>16338</v>
+        <v>17026</v>
       </c>
       <c r="R89" t="n">
-        <v>60.00639950731433</v>
+        <v>62.53329403914395</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>160649</v>
+        <v>161337</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>17026</v>
+        <v>17268</v>
       </c>
       <c r="O89" t="n">
-        <v>17026</v>
+        <v>17268</v>
       </c>
       <c r="R89" t="n">
-        <v>62.53329403914395</v>
+        <v>63.42211449946773</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>161337</v>
+        <v>161579</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -13855,12 +13855,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13894,95 +13894,78 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>130</v>
+        <v>356</v>
       </c>
       <c r="O75" t="n">
-        <v>130</v>
-      </c>
-      <c r="R75" t="n">
-        <v>2.312451922123379</v>
+        <v>356</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14009,17 +13992,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14053,170 +14036,78 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>130</v>
+        <v>11805</v>
       </c>
       <c r="O76" t="n">
-        <v>130</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>RSV</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
+        <v>11805</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14248,12 +14139,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -14278,7 +14169,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -14287,17 +14178,14 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>737</v>
+        <v>55</v>
       </c>
       <c r="O77" t="n">
-        <v>737</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0.6019877963759698</v>
+        <v>55</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -14326,42 +14214,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14393,12 +14281,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14423,7 +14311,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -14432,17 +14320,14 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>682</v>
+        <v>3494</v>
       </c>
       <c r="O78" t="n">
-        <v>682</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.5570633339598525</v>
+        <v>3494</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -14471,42 +14356,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14538,12 +14423,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14568,7 +14453,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -14577,17 +14462,14 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>788</v>
+        <v>1261</v>
       </c>
       <c r="O79" t="n">
-        <v>788</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.6436450251618239</v>
+        <v>1261</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -14616,42 +14498,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14683,12 +14565,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14713,7 +14595,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -14722,17 +14604,14 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>885</v>
+        <v>414</v>
       </c>
       <c r="O80" t="n">
-        <v>885</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.7228754406957031</v>
+        <v>414</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -14761,42 +14640,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14828,12 +14707,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14858,26 +14737,23 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27444</v>
+        <v>6251</v>
       </c>
       <c r="O81" t="n">
-        <v>27444</v>
-      </c>
-      <c r="R81" t="n">
-        <v>100.7966475749011</v>
+        <v>6251</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -14911,12 +14787,12 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -14931,12 +14807,12 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -14973,12 +14849,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15003,104 +14879,87 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>22</v>
+        <v>1910</v>
       </c>
       <c r="O82" t="n">
-        <v>22</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.3913380175901103</v>
+        <v>1910</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15127,7 +14986,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15162,112 +15021,37 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="O83" t="n">
-        <v>22</v>
+        <v>130</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2.312451922123379</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1170</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>RSV</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN83" t="b">
-        <v>1</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -15361,17 +15145,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15396,90 +15180,179 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>764</v>
+        <v>130</v>
       </c>
       <c r="O84" t="n">
-        <v>764</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0.6240416233802455</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>130</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15541,22 +15414,22 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>826</v>
+        <v>737</v>
       </c>
       <c r="O85" t="n">
-        <v>826</v>
+        <v>737</v>
       </c>
       <c r="R85" t="n">
-        <v>0.674683744649323</v>
+        <v>0.6019877963759698</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15686,22 +15559,22 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>976</v>
+        <v>682</v>
       </c>
       <c r="O86" t="n">
-        <v>976</v>
+        <v>682</v>
       </c>
       <c r="R86" t="n">
-        <v>0.7972050057841878</v>
+        <v>0.5570633339598525</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15831,22 +15704,22 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1082</v>
+        <v>788</v>
       </c>
       <c r="O87" t="n">
-        <v>1082</v>
+        <v>788</v>
       </c>
       <c r="R87" t="n">
-        <v>0.8837866969861591</v>
+        <v>0.6436450251618239</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15976,22 +15849,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1027</v>
+        <v>885</v>
       </c>
       <c r="O88" t="n">
-        <v>1027</v>
+        <v>885</v>
       </c>
       <c r="R88" t="n">
-        <v>0.8388622345700421</v>
+        <v>0.7228754406957031</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -16121,22 +15994,22 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>17268</v>
+        <v>27446</v>
       </c>
       <c r="O89" t="n">
-        <v>17268</v>
+        <v>27446</v>
       </c>
       <c r="R89" t="n">
-        <v>63.42211449946773</v>
+        <v>100.8039931985402</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16236,12 +16109,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16266,104 +16139,87 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>526</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.03557618341728275</v>
+        <v>526</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16390,17 +16246,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16425,179 +16281,87 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>9272</v>
       </c>
       <c r="O91" t="n">
-        <v>2</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>RSV</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD91" t="inlineStr">
+        <v>9272</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AT91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV91" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16629,12 +16393,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16659,26 +16423,23 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1155</v>
+        <v>94</v>
       </c>
       <c r="O92" t="n">
-        <v>1155</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.94341371073846</v>
+        <v>94</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -16707,42 +16468,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16535,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16804,26 +16565,23 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1417</v>
+        <v>3336</v>
       </c>
       <c r="O93" t="n">
-        <v>1417</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1.157417513520691</v>
+        <v>3336</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -16852,42 +16610,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16919,12 +16677,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16949,26 +16707,23 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1067</v>
+        <v>3009</v>
       </c>
       <c r="O94" t="n">
-        <v>1067</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.8715345708726727</v>
+        <v>3009</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -16997,42 +16752,4378 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>767</v>
+      </c>
+      <c r="O95" t="n">
+        <v>767</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>7512</v>
+      </c>
+      <c r="O96" t="n">
+        <v>7512</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>2928</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2928</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>22</v>
+      </c>
+      <c r="O98" t="n">
+        <v>22</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.3913380175901103</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>22</v>
+      </c>
+      <c r="O99" t="n">
+        <v>22</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>764</v>
+      </c>
+      <c r="O100" t="n">
+        <v>764</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.6240416233802455</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW94" t="inlineStr">
+      <c r="AW100" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
+      <c r="AX100" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY94" t="inlineStr">
+      <c r="AY100" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA94" t="inlineStr">
+      <c r="BA100" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB94" t="inlineStr">
+      <c r="BB100" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC94" t="inlineStr">
+      <c r="BC100" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>826</v>
+      </c>
+      <c r="O101" t="n">
+        <v>826</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.674683744649323</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>976</v>
+      </c>
+      <c r="O102" t="n">
+        <v>976</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.7972050057841878</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>1082</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1082</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.8837866969861591</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>1027</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1027</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.8388622345700421</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>18795</v>
+      </c>
+      <c r="O105" t="n">
+        <v>18795</v>
+      </c>
+      <c r="R105" t="n">
+        <v>69.03049814787445</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>585</v>
+      </c>
+      <c r="O106" t="n">
+        <v>585</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5568</v>
+      </c>
+      <c r="O107" t="n">
+        <v>5568</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>92</v>
+      </c>
+      <c r="O108" t="n">
+        <v>92</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2381</v>
+      </c>
+      <c r="O109" t="n">
+        <v>2381</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2539</v>
+      </c>
+      <c r="O110" t="n">
+        <v>2539</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>455</v>
+      </c>
+      <c r="O111" t="n">
+        <v>455</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>4048</v>
+      </c>
+      <c r="O112" t="n">
+        <v>4048</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1777</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1777</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" t="n">
+        <v>2</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" t="n">
+        <v>2</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1155</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1155</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.94341371073846</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>1417</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1417</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.157417513520691</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1067</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1067</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.8715345708726727</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>1090</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1090</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.8903211642466852</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>547</v>
+      </c>
+      <c r="O120" t="n">
+        <v>547</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2.009028065277325</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17069,7 +21160,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -17152,7 +21243,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -17162,7 +21253,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -17182,7 +21273,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -17214,7 +21305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>161579</v>
+        <v>235180</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>18795</v>
+        <v>18819</v>
       </c>
       <c r="O105" t="n">
-        <v>18795</v>
+        <v>18819</v>
       </c>
       <c r="R105" t="n">
-        <v>69.03049814787445</v>
+        <v>69.11864563154293</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20656,13 +20656,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>547</v>
+        <v>1071</v>
       </c>
       <c r="O120" t="n">
-        <v>547</v>
+        <v>1071</v>
       </c>
       <c r="R120" t="n">
-        <v>2.009028065277325</v>
+        <v>3.933581458705695</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235180</v>
+        <v>235728</v>
       </c>
     </row>
     <row r="16">
